--- a/guidelines/Nova Data_dict_Students.xlsx
+++ b/guidelines/Nova Data_dict_Students.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eliaskarle/Coding/Nova/BusinessCases_1/Business_Case_BNP/guidelines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42E3E94-DE16-0844-81FD-3FE581C032AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E79D537-B82E-934D-93C9-3BFF2CA19821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3440" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{F44BA817-83E8-4B28-B840-7082C63E8482}"/>
+    <workbookView xWindow="-3440" yWindow="-21100" windowWidth="38400" windowHeight="21100" activeTab="4" xr2:uid="{F44BA817-83E8-4B28-B840-7082C63E8482}"/>
   </bookViews>
   <sheets>
     <sheet name="BDOSSTOTAL" sheetId="1" r:id="rId1"/>
     <sheet name="CRC" sheetId="4" r:id="rId2"/>
     <sheet name="CredScore" sheetId="3" r:id="rId3"/>
     <sheet name="FAMA_LIGHT_" sheetId="2" r:id="rId4"/>
+    <sheet name="Feature Engineering" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BDOSSTOTAL!$A$1:$L$35</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="494">
   <si>
     <t>libname</t>
   </si>
@@ -1267,14 +1268,380 @@
     <t>Spalte1</t>
   </si>
   <si>
+    <t>Spalte2</t>
+  </si>
+  <si>
     <t>Name2</t>
+  </si>
+  <si>
+    <t>Feature Engineering Proposals — Early Settlement &amp; Churn Prediction</t>
+  </si>
+  <si>
+    <t>Early Settler: borrower repays loan before contractual end date  |  Churn: ≥1 active contract in reference month → 0 active contracts within 30 days</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Feature Name</t>
+  </si>
+  <si>
+    <t>Source Tables</t>
+  </si>
+  <si>
+    <t>Formula / Logic</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>Early Settler</t>
+  </si>
+  <si>
+    <t>Churn</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Contract Maturity &amp; Repayment</t>
+  </si>
+  <si>
+    <t>REPAYMENT_RATIO</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>CONTRACT_AGE_MONTHS</t>
+  </si>
+  <si>
+    <t>How long the contract has been active. Early settlers tend to prepay mid-contract. Churners may leave after a predictable tenure.</t>
+  </si>
+  <si>
+    <t>REMAINING_TERM_MONTHS</t>
+  </si>
+  <si>
+    <t>(MTFINO − CRD) / MTFINO</t>
+  </si>
+  <si>
+    <t>Fraction of principal already repaid. Early settlers show accelerating repayment — a high ratio with many months remaining is a strong early settlement signal.</t>
+  </si>
+  <si>
+    <t>DPOS − DCREAT (converted to months)</t>
+  </si>
+  <si>
+    <t>Derive from MTFIN / MENSALIDADE or DURDEG − elapsed months</t>
+  </si>
+  <si>
+    <t>Estimated months to contractual maturity. Short remaining terms + high CRD reduction speed flag early settlement.</t>
+  </si>
+  <si>
+    <t>LIFECYCLE_RATIO</t>
+  </si>
+  <si>
+    <t>CONTRACT_AGE / (CONTRACT_AGE + REMAINING_TERM)</t>
+  </si>
+  <si>
+    <t>Fraction of contract lifecycle elapsed (0 to 1). Values near 0.4-0.7 with strong repayment ratios are the sweet spot for early settlement.</t>
+  </si>
+  <si>
+    <t>OVERPAYMENT_RATIO</t>
+  </si>
+  <si>
+    <t>MENSALIDADE_CORR / MENSALIDADE</t>
+  </si>
+  <si>
+    <t>Whether current instalment exceeds the original. Ratios &gt; 1 suggest voluntary overpayments — a direct early settlement precursor.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Payment Behavior</t>
+  </si>
+  <si>
+    <t>REGULARIZATION_COMPLETION</t>
+  </si>
+  <si>
+    <t>RANGPRO / DURDEG</t>
+  </si>
+  <si>
+    <t>Fraction of agreed regularizations paid. High = disciplined borrower, likely to settle early. Low = risk signal for both models.</t>
+  </si>
+  <si>
+    <t>DELAY_INTENSITY</t>
+  </si>
+  <si>
+    <t>RANGCLI / CONTRACT_AGE_MONTHS</t>
+  </si>
+  <si>
+    <t>Payment delays normalized by contract age. Separates chronic late-payers from one-off incidents. Higher values predict churn via dispute paths.</t>
+  </si>
+  <si>
+    <t>RISK_TREND_3M</t>
+  </si>
+  <si>
+    <t>Compare last 3 chars vs prior 3 chars of RISK string</t>
+  </si>
+  <si>
+    <t>Whether risk position is improving, stable, or deteriorating. Improving trends correlate with early settlement; worsening trends predict churn.</t>
+  </si>
+  <si>
+    <t>RISK_VOLATILITY_12M</t>
+  </si>
+  <si>
+    <t>Count risk-position changes in last 12 chars of RISK</t>
+  </si>
+  <si>
+    <t>How often risk classification flipped in 12 months. High volatility = unstable (churn). Low + good position = early settler.</t>
+  </si>
+  <si>
+    <t>MONTHS_AT_CURRENT_RISK</t>
+  </si>
+  <si>
+    <t>Count trailing identical chars in RISK string</t>
+  </si>
+  <si>
+    <t>Consecutive months at current risk level. Long stable at good risk = early settlement candidate. Long stable at bad risk = churn.</t>
+  </si>
+  <si>
+    <t>Financial Capacity</t>
+  </si>
+  <si>
+    <t>DTI_RATIO</t>
+  </si>
+  <si>
+    <t>BDOSSTOTAL + CRC</t>
+  </si>
+  <si>
+    <t>MENSALIDADE / RESSO (internal) or MT_MENSAL / RESSO (total)</t>
+  </si>
+  <si>
+    <t>Debt-to-income ratio. Low DTI = more disposable income = capacity to settle early. Very high DTI = financial stress = churn risk.</t>
+  </si>
+  <si>
+    <t>TOTAL_DEBT_BURDEN</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>DIVIDAS_CL + DIVIDAS_CP + DIVIDAS_AUTO + DIVIDAS_HT</t>
+  </si>
+  <si>
+    <t>Total debt across all lenders. High external leverage reduces capacity for early settlement and increases churn probability.</t>
+  </si>
+  <si>
+    <t>EXTERNAL_OVERDUE_FLAG</t>
+  </si>
+  <si>
+    <t>1 if any MONTVENC &gt; 0, else 0</t>
+  </si>
+  <si>
+    <t>Whether client has overdue amounts at other lenders. Externally delinquent clients are significantly more likely to churn. Unlikely to settle early.</t>
+  </si>
+  <si>
+    <t>INSTALMENT_TO_CAPITAL</t>
+  </si>
+  <si>
+    <t>MENSALIDADE / CRD</t>
+  </si>
+  <si>
+    <t>Monthly payment as fraction of remaining capital. High ratio = fast paydown trajectory, strong early settlement signal.</t>
+  </si>
+  <si>
+    <t>INCOME_BUFFER</t>
+  </si>
+  <si>
+    <t>(RESSO - MENSALIDADE) / RESSO</t>
+  </si>
+  <si>
+    <t>Share of income remaining after instalment. Larger buffer = more flexibility = higher early settlement probability.</t>
+  </si>
+  <si>
+    <t>Portfolio &amp; Relationship</t>
+  </si>
+  <si>
+    <t>MULTI_PRODUCT_FLAG</t>
+  </si>
+  <si>
+    <t>FAMA_LIGHT_</t>
+  </si>
+  <si>
+    <t>1 if (ALLBD_N_CL + ALLBD_N_CP) &gt; 1, else 0</t>
+  </si>
+  <si>
+    <t>Clients with multiple products have deeper relationships and are less likely to churn. Single-product clients who settle may be churning simultaneously.</t>
+  </si>
+  <si>
+    <t>ACTIVE_CONTRACT_COUNT</t>
+  </si>
+  <si>
+    <t>ALLBD_A_CL__N + ALLBD_A_CP__N</t>
+  </si>
+  <si>
+    <t>Total active contracts. Directly feeds churn definition (0 = churned). Early settlers with only 1 active contract are high churn risk.</t>
+  </si>
+  <si>
+    <t>RELATIONSHIP_TENURE</t>
+  </si>
+  <si>
+    <t>ALLBD_IDADE_MSA__N (max contract antiquity)</t>
+  </si>
+  <si>
+    <t>Duration of longest relationship. Long-tenure clients are stickier (less churn) but may also know prepayment options better.</t>
+  </si>
+  <si>
+    <t>NEW_CONTRACT_RECENCY</t>
+  </si>
+  <si>
+    <t>ALLBD_IDADE_MIN__N (min contract antiquity)</t>
+  </si>
+  <si>
+    <t>Months since most recent contract. Very recent = still engaged. Long gap = disengaging (churn signal).</t>
+  </si>
+  <si>
+    <t>EVENT_FREQUENCY</t>
+  </si>
+  <si>
+    <t>ALLBD_N_events__N / ALLBD_IDADE_MEAN__N</t>
+  </si>
+  <si>
+    <t>Contract modifications per month of avg contract age. Frequent mods can signal proactive management (settler) or distress (churn).</t>
+  </si>
+  <si>
+    <t>External Credit</t>
+  </si>
+  <si>
+    <t>CREDIT_CONCENTRATION</t>
+  </si>
+  <si>
+    <t>COUNT_CL / COUNT_TOTAL</t>
+  </si>
+  <si>
+    <t>Share of credit portfolio in consumer lending. High concentration = dependency on this credit type, relevant for churn path and settlement behavior.</t>
+  </si>
+  <si>
+    <t>WRITEOFF_HISTORY_FLAG</t>
+  </si>
+  <si>
+    <t>1 if any MONTABATV &gt; 0, else 0</t>
+  </si>
+  <si>
+    <t>Whether client has historical write-offs at any lender. Strong negative signal: unlikely to settle early, elevated churn/default risk.</t>
+  </si>
+  <si>
+    <t>OVERDUE_TO_DEBT_RATIO</t>
+  </si>
+  <si>
+    <t>SUM(all MONTVENC) / SUM(all DIVIDAS)</t>
+  </si>
+  <si>
+    <t>Fraction of total external debt that is overdue. Measures severity of delinquency across the board. High ratio = churn/default path.</t>
+  </si>
+  <si>
+    <t>Scoring &amp; Risk</t>
+  </si>
+  <si>
+    <t>BEHAVIORAL_SCORE_NUM</t>
+  </si>
+  <si>
+    <t>CredScore</t>
+  </si>
+  <si>
+    <t>Map kp_sqe: A=1, B=2, ..., X=24; null=25</t>
+  </si>
+  <si>
+    <t>Numeric encoding of behavioral score for model consumption. Top scores (A-D) correlate with early settlement; bottom scores with churn.</t>
+  </si>
+  <si>
+    <t>SCORE_RISK_MISMATCH</t>
+  </si>
+  <si>
+    <t>CredScore + BDOSSTOTAL</t>
+  </si>
+  <si>
+    <t>1 if kp_sqe is good (A-E) but RISKA is high</t>
+  </si>
+  <si>
+    <t>Divergence between behavioral score and current risk position. Mismatches indicate rapid deterioration — a strong churn predictor.</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>AGE_BUCKET</t>
+  </si>
+  <si>
+    <t>Bin sdem_age: &lt;25, 25-34, 35-44, 45-54, 55-64, 65+</t>
+  </si>
+  <si>
+    <t>Age brackets have distinct prepayment and churn patterns. Younger clients churn more; mid-career with stable income settle early more often.</t>
+  </si>
+  <si>
+    <t>HOUSING_STABILITY_SCORE</t>
+  </si>
+  <si>
+    <t>Owner(P)=3, Mortgage(A)=2, Family(F)=2, Tenant(L)=1, Other=0</t>
+  </si>
+  <si>
+    <t>Numeric stability proxy from housing. Homeowners are more financially stable (less churn, more capacity for early settlement).</t>
+  </si>
+  <si>
+    <t>IS_PARTNERED</t>
+  </si>
+  <si>
+    <t>1 if sdem_SITFAM in (C, U), else 0</t>
+  </si>
+  <si>
+    <t>Partnered/married clients tend to have dual incomes and higher stability. Relevant for affordability (early settlement) and retention (churn).</t>
+  </si>
+  <si>
+    <t>Composite Scores</t>
+  </si>
+  <si>
+    <t>EARLY_SETTLE_PROPENSITY</t>
+  </si>
+  <si>
+    <t>All tables</t>
+  </si>
+  <si>
+    <t>Weighted: 0.3*REPAYMENT_RATIO + 0.2*(1-DTI) + 0.2*LIFECYCLE + 0.15*OVERPAY + 0.15*BEHAV_SCORE</t>
+  </si>
+  <si>
+    <t>Composite early settlement propensity combining repayment progress, financial capacity, contract maturity, and credit quality into one score.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>CHURN_RISK_COMPOSITE</t>
+  </si>
+  <si>
+    <t>Weighted: 0.25*DELAY + 0.2*EXT_OVERDUE + 0.2*(1-ACTIVE_norm) + 0.2*RISK_TREND + 0.15*DTI</t>
+  </si>
+  <si>
+    <t>Composite churn risk combining payment behavior, external delinquency, relationship depth, risk trajectory, and financial stress.</t>
+  </si>
+  <si>
+    <t>xLow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How long the contract has been active. Early settlers tend to prepay mid-contract. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1351,8 +1718,73 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0E2841"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1364,8 +1796,44 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E2841"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1478,12 +1946,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF64BEE6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF64BEE6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1628,12 +2114,165 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Neutral 2" xfId="1" xr:uid="{EE3F8DD8-3C8F-4F8F-851B-4C30274C96A6}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0E2841"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color rgb="FF64BEE6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2755,72 +3394,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C3F1D3AE-F5B8-EA44-8885-9358133A6D7B}" name="Tabelle4" displayName="Tabelle4" ref="C1:L35" totalsRowShown="0" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C3F1D3AE-F5B8-EA44-8885-9358133A6D7B}" name="Tabelle4" displayName="Tabelle4" ref="C1:L35" totalsRowShown="0" tableBorderDxfId="34">
   <autoFilter ref="C1:L35" xr:uid="{C3F1D3AE-F5B8-EA44-8885-9358133A6D7B}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{D6C1F963-0EA8-4A46-B1B8-320581389A93}" name="Rank" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{79705122-9E31-2040-9005-A61D04B29D48}" name="name" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{3A07F526-BF46-7A43-B4F1-D78B9C6D47A9}" name="name detailed" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{93FC5D1D-9753-544A-8547-598AC93780BE}" name="Description" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{D382E99C-4369-1A4B-8AD5-386DEB9D9CD8}" name="Description Detailed" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{D6C1F963-0EA8-4A46-B1B8-320581389A93}" name="Rank" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{79705122-9E31-2040-9005-A61D04B29D48}" name="name" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{3A07F526-BF46-7A43-B4F1-D78B9C6D47A9}" name="name detailed" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{93FC5D1D-9753-544A-8547-598AC93780BE}" name="Description" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{D382E99C-4369-1A4B-8AD5-386DEB9D9CD8}" name="Description Detailed" dataDxfId="29"/>
     <tableColumn id="6" xr3:uid="{120CE31D-65F8-E849-88F9-1322E4C1763A}" name="possible values"/>
-    <tableColumn id="7" xr3:uid="{F16C8376-45AB-D74B-AFCC-92D97BBC73EB}" name="type" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{D4072A66-1301-1F47-8291-AC8BB4E4C0BF}" name="length" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{EF101C5F-8285-4E4D-8E0A-895551434BEE}" name="varnum" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{C4E2291E-5585-AF46-86D7-647A97233C7C}" name="Personal Data" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{F16C8376-45AB-D74B-AFCC-92D97BBC73EB}" name="type" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{D4072A66-1301-1F47-8291-AC8BB4E4C0BF}" name="length" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{EF101C5F-8285-4E4D-8E0A-895551434BEE}" name="varnum" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{C4E2291E-5585-AF46-86D7-647A97233C7C}" name="Personal Data" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0C2DB7C4-3F5A-4D47-B02F-0BAAE34E37A4}" name="Tabelle3" displayName="Tabelle3" ref="A1:F23" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0C2DB7C4-3F5A-4D47-B02F-0BAAE34E37A4}" name="Tabelle3" displayName="Tabelle3" ref="A1:F23" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" tableBorderDxfId="43">
   <autoFilter ref="A1:F23" xr:uid="{0C2DB7C4-3F5A-4D47-B02F-0BAAE34E37A4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{026812A5-86D8-E04B-97D2-A04E0198D4E3}" name="Rank" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{9442FC44-40E1-E145-9DFD-47375FC85AF0}" name="Name" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{6A32465F-BE7B-1A42-823A-864742016A8D}" name="name (English)" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{0E62FB61-E72B-AD4E-8735-C516D7F14C4D}" name="Info" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{DBCB9CDD-8F7D-604F-83AC-DE308D92EF1D}" name="Description Detailed" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{9DB1857C-CDBA-A04A-8D57-BACC5B415AE7}" name="Type" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{026812A5-86D8-E04B-97D2-A04E0198D4E3}" name="Rank" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{9442FC44-40E1-E145-9DFD-47375FC85AF0}" name="Name" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{6A32465F-BE7B-1A42-823A-864742016A8D}" name="name (English)" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{0E62FB61-E72B-AD4E-8735-C516D7F14C4D}" name="Info" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{DBCB9CDD-8F7D-604F-83AC-DE308D92EF1D}" name="Description Detailed" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{9DB1857C-CDBA-A04A-8D57-BACC5B415AE7}" name="Type" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A8D3F384-B34B-4049-A41A-E2B68B32A3DD}" name="Tabelle6" displayName="Tabelle6" ref="A1:G10" totalsRowShown="0" headerRowDxfId="19" dataDxfId="20">
-  <autoFilter ref="A1:G10" xr:uid="{A8D3F384-B34B-4049-A41A-E2B68B32A3DD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A8D3F384-B34B-4049-A41A-E2B68B32A3DD}" name="Tabelle6" displayName="Tabelle6" ref="A1:G7" totalsRowShown="0" headerRowDxfId="23" dataDxfId="24">
+  <autoFilter ref="A1:G7" xr:uid="{A8D3F384-B34B-4049-A41A-E2B68B32A3DD}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6EDF13ED-B98C-4B42-9823-E5316E2BB627}" name="Rank" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{2C65BA03-6AB0-DE4A-9A2F-606A9E955526}" name="Name2" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{8569D98A-9D3D-9B47-9B59-1DEC7328C603}" name="name (English)" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{AE30A4BB-D70B-A44B-B6F3-A90AFC8B01B5}" name="Type" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{281B71CC-1F7F-B645-B0FB-6E89548E2B83}" name="Label" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{C5622231-D5D7-6C47-9325-94F2D9C3D9B2}" name="Info" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{CC6A1933-1EAA-E548-9484-844A88B0B118}" name="Description Detailed" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{6EDF13ED-B98C-4B42-9823-E5316E2BB627}" name="Rank" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{2C65BA03-6AB0-DE4A-9A2F-606A9E955526}" name="Name2" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{8569D98A-9D3D-9B47-9B59-1DEC7328C603}" name="name (English)" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{AE30A4BB-D70B-A44B-B6F3-A90AFC8B01B5}" name="Type" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{281B71CC-1F7F-B645-B0FB-6E89548E2B83}" name="Label" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{C5622231-D5D7-6C47-9325-94F2D9C3D9B2}" name="Info" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{CC6A1933-1EAA-E548-9484-844A88B0B118}" name="Description Detailed" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C3C7F790-6419-EB44-95C0-6CBA53D532B9}" name="Tabelle7" displayName="Tabelle7" ref="A1:K25" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:K25" xr:uid="{C3C7F790-6419-EB44-95C0-6CBA53D532B9}"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C3C7F790-6419-EB44-95C0-6CBA53D532B9}" name="Tabelle7" displayName="Tabelle7" ref="A1:L24" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5">
+  <autoFilter ref="A1:L24" xr:uid="{C3C7F790-6419-EB44-95C0-6CBA53D532B9}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{BE8DAACD-9D95-BD4A-A406-C65169DC74E4}" name="Rank"/>
-    <tableColumn id="2" xr3:uid="{F05175D1-70C4-CE45-856F-4CE1A533878D}" name="Name" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{BF87B394-885D-5B4F-8627-57C45916CF2C}" name="name (English)" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{449294EE-FAC6-DE47-8E1B-4C1256393C1E}" name="Type" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{459E15DD-7EE2-0340-9F91-7A67DE597898}" name="Length" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{BD549E53-4638-6448-B22C-DFF34283BB3C}" name="Format" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{02DFAAE9-1A7A-7844-95D5-42E6DB2CA868}" name="Informat" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{6E60A3AC-C0F3-3B44-8632-292ED79E3B0D}" name="Label" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{8F14B3CF-32A4-E846-A66B-6F64540940D3}" name="Info" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{3E1C27CA-A773-4547-BA1E-40491512C666}" name="Description Detailed" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{58855DB6-0B97-8C4C-BD71-F415683C86FB}" name="Spalte1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{F05175D1-70C4-CE45-856F-4CE1A533878D}" name="Name" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{BF87B394-885D-5B4F-8627-57C45916CF2C}" name="name (English)" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{449294EE-FAC6-DE47-8E1B-4C1256393C1E}" name="Type" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{459E15DD-7EE2-0340-9F91-7A67DE597898}" name="Length" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{BD549E53-4638-6448-B22C-DFF34283BB3C}" name="Format" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{02DFAAE9-1A7A-7844-95D5-42E6DB2CA868}" name="Informat" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{6E60A3AC-C0F3-3B44-8632-292ED79E3B0D}" name="Label" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{8F14B3CF-32A4-E846-A66B-6F64540940D3}" name="Info" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{3E1C27CA-A773-4547-BA1E-40491512C666}" name="Description Detailed" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{58855DB6-0B97-8C4C-BD71-F415683C86FB}" name="Spalte1" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{77EB01B7-1349-794D-8B61-37094C0ADEE1}" name="Spalte2" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{7DC9A272-D4DD-6143-8688-AD4C8DB1B094}" name="Tabelle8" displayName="Tabelle8" ref="A4:I34" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A4:I34" xr:uid="{7DC9A272-D4DD-6143-8688-AD4C8DB1B094}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:I34">
+    <sortCondition ref="I4:I34"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A076CD85-20F9-B44D-ADFE-0EB8D6A2DD3A}" name="#"/>
+    <tableColumn id="2" xr3:uid="{C312FC7D-2E5E-3648-9B6B-CAAB63D47F16}" name="Category"/>
+    <tableColumn id="3" xr3:uid="{81E638A2-4973-2445-9A92-237A6DA7048C}" name="Feature Name"/>
+    <tableColumn id="4" xr3:uid="{6576228F-5BD0-594C-8CF7-3A00731A8844}" name="Source Tables"/>
+    <tableColumn id="5" xr3:uid="{B5367025-FB81-5347-A308-20FAB7B9C5B9}" name="Formula / Logic"/>
+    <tableColumn id="6" xr3:uid="{853B3A18-65ED-BA48-9326-09436CD88C3F}" name="Rationale"/>
+    <tableColumn id="7" xr3:uid="{4847192C-36BF-A14E-90C9-B3711DECDC4E}" name="Early Settler"/>
+    <tableColumn id="8" xr3:uid="{B2446D20-9C90-BE46-9058-1552A043F675}" name="Churn"/>
+    <tableColumn id="9" xr3:uid="{D54C4D0E-D03E-A047-BBDB-8D7B78F85037}" name="Priority"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3683,7 +4344,7 @@
       <c r="F15" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="53" t="s">
         <v>250</v>
       </c>
       <c r="H15" s="23"/>
@@ -4473,7 +5134,9 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
       <c r="B3" s="6" t="s">
         <v>54</v>
       </c>
@@ -4492,7 +5155,9 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
       <c r="B4" s="6" t="s">
         <v>103</v>
       </c>
@@ -4510,7 +5175,9 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
+      <c r="A5" s="9">
+        <v>3</v>
+      </c>
       <c r="B5" s="6" t="s">
         <v>104</v>
       </c>
@@ -4546,7 +5213,9 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
+      <c r="A7" s="9">
+        <v>4</v>
+      </c>
       <c r="B7" s="6" t="s">
         <v>106</v>
       </c>
@@ -4636,7 +5305,9 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
+      <c r="A12" s="9">
+        <v>5</v>
+      </c>
       <c r="B12" s="6" t="s">
         <v>111</v>
       </c>
@@ -4672,7 +5343,9 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
+      <c r="A14" s="9">
+        <v>6</v>
+      </c>
       <c r="B14" s="6" t="s">
         <v>113</v>
       </c>
@@ -5008,7 +5681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6223C38-9B3F-4646-B590-A056E0FC0454}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
@@ -5025,7 +5698,7 @@
         <v>198</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1" s="41" t="s">
         <v>200</v>
@@ -5045,149 +5718,143 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="51"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="B2" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>53</v>
+      </c>
       <c r="E2" s="45"/>
       <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="51"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="D4" s="45" t="s">
+      <c r="B3" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>359</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="41"/>
+      <c r="G3" s="44" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="51">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="41"/>
+      <c r="G4" s="44" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="51"/>
+      <c r="B5" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>361</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="41"/>
+      <c r="G5" s="44" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="51">
+        <v>2</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A7" s="51">
+        <v>3</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>363</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="H4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="51"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="51"/>
-      <c r="B6" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>359</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="44" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
-      <c r="B7" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>360</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>55</v>
-      </c>
       <c r="E7" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" s="41"/>
+        <v>164</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>197</v>
+      </c>
       <c r="G7" s="44" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>361</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="44" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="51"/>
-      <c r="B9" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>362</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A10" s="51"/>
-      <c r="B10" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="G10" s="44" t="s">
         <v>369</v>
       </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -5253,21 +5920,6 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -5280,7 +5932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD903F7F-41C9-4E0A-AC58-492487590BE8}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
@@ -5328,6 +5980,9 @@
       <c r="K1" s="47" t="s">
         <v>370</v>
       </c>
+      <c r="L1" s="52" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" s="47" t="s">
@@ -5350,54 +6005,68 @@
         <v>294</v>
       </c>
       <c r="K2" s="49"/>
-      <c r="L2" t="s">
+      <c r="L2" s="52" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
+    <row r="3" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="B3" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="47">
+        <v>8</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>56</v>
+      </c>
       <c r="G3" s="47"/>
       <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
+      <c r="I3" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="48" t="s">
+        <v>295</v>
+      </c>
       <c r="K3" s="49"/>
+      <c r="L3" s="52"/>
     </row>
     <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B4" s="47" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E4" s="47">
         <v>8</v>
       </c>
-      <c r="F4" s="47" t="s">
-        <v>56</v>
-      </c>
+      <c r="F4" s="47"/>
       <c r="G4" s="47"/>
       <c r="H4" s="47"/>
       <c r="I4" s="47" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="J4" s="48" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K4" s="49"/>
+      <c r="L4" s="52"/>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B5" s="47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>53</v>
@@ -5409,19 +6078,20 @@
       <c r="G5" s="47"/>
       <c r="H5" s="47"/>
       <c r="I5" s="47" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="J5" s="48" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K5" s="49"/>
+      <c r="L5" s="52"/>
     </row>
     <row r="6" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B6" s="47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>53</v>
@@ -5433,19 +6103,20 @@
       <c r="G6" s="47"/>
       <c r="H6" s="47"/>
       <c r="I6" s="47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J6" s="48" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K6" s="49"/>
+      <c r="L6" s="52"/>
     </row>
     <row r="7" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B7" s="47" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>53</v>
@@ -5457,19 +6128,20 @@
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
       <c r="I7" s="47" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K7" s="49"/>
+      <c r="L7" s="52"/>
     </row>
     <row r="8" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B8" s="47" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>53</v>
@@ -5481,19 +6153,20 @@
       <c r="G8" s="47"/>
       <c r="H8" s="47"/>
       <c r="I8" s="47" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J8" s="48" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K8" s="49"/>
+      <c r="L8" s="52"/>
     </row>
     <row r="9" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B9" s="47" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>53</v>
@@ -5505,19 +6178,20 @@
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
       <c r="I9" s="47" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="J9" s="48" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K9" s="49"/>
+      <c r="L9" s="52"/>
     </row>
     <row r="10" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B10" s="47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>53</v>
@@ -5529,19 +6203,20 @@
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
       <c r="I10" s="47" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="J10" s="48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K10" s="49"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B11" s="47" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>53</v>
@@ -5553,19 +6228,20 @@
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
       <c r="I11" s="47" t="s">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="J11" s="48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K11" s="49"/>
+      <c r="L11" s="52"/>
     </row>
     <row r="12" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B12" s="47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>53</v>
@@ -5577,19 +6253,20 @@
       <c r="G12" s="47"/>
       <c r="H12" s="47"/>
       <c r="I12" s="47" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="J12" s="48" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K12" s="49"/>
+      <c r="L12" s="52"/>
     </row>
     <row r="13" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B13" s="47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>53</v>
@@ -5601,19 +6278,20 @@
       <c r="G13" s="47"/>
       <c r="H13" s="47"/>
       <c r="I13" s="47" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J13" s="48" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K13" s="49"/>
+      <c r="L13" s="52"/>
     </row>
     <row r="14" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B14" s="47" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>53</v>
@@ -5625,19 +6303,20 @@
       <c r="G14" s="47"/>
       <c r="H14" s="47"/>
       <c r="I14" s="47" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J14" s="48" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K14" s="49"/>
+      <c r="L14" s="52"/>
     </row>
     <row r="15" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B15" s="47" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D15" s="47" t="s">
         <v>53</v>
@@ -5649,19 +6328,20 @@
       <c r="G15" s="47"/>
       <c r="H15" s="47"/>
       <c r="I15" s="47" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J15" s="48" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K15" s="49"/>
-    </row>
-    <row r="16" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="L15" s="52"/>
+    </row>
+    <row r="16" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="B16" s="47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>53</v>
@@ -5673,19 +6353,20 @@
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
       <c r="I16" s="47" t="s">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="J16" s="48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K16" s="49"/>
-    </row>
-    <row r="17" spans="2:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="L16" s="52"/>
+    </row>
+    <row r="17" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="B17" s="47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>53</v>
@@ -5697,19 +6378,20 @@
       <c r="G17" s="47"/>
       <c r="H17" s="47"/>
       <c r="I17" s="47" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="J17" s="48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K17" s="49"/>
-    </row>
-    <row r="18" spans="2:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="L17" s="52"/>
+    </row>
+    <row r="18" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="B18" s="47" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D18" s="47" t="s">
         <v>53</v>
@@ -5721,19 +6403,20 @@
       <c r="G18" s="47"/>
       <c r="H18" s="47"/>
       <c r="I18" s="47" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J18" s="48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K18" s="49"/>
-    </row>
-    <row r="19" spans="2:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="L18" s="52"/>
+    </row>
+    <row r="19" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="B19" s="47" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>53</v>
@@ -5745,19 +6428,20 @@
       <c r="G19" s="47"/>
       <c r="H19" s="47"/>
       <c r="I19" s="47" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J19" s="48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K19" s="49"/>
-    </row>
-    <row r="20" spans="2:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="L19" s="52"/>
+    </row>
+    <row r="20" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="B20" s="47" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>53</v>
@@ -5769,19 +6453,23 @@
       <c r="G20" s="47"/>
       <c r="H20" s="47"/>
       <c r="I20" s="47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J20" s="48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K20" s="49"/>
-    </row>
-    <row r="21" spans="2:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="L20" s="52"/>
+    </row>
+    <row r="21" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1</v>
+      </c>
       <c r="B21" s="47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D21" s="47" t="s">
         <v>53</v>
@@ -5793,43 +6481,53 @@
       <c r="G21" s="47"/>
       <c r="H21" s="47"/>
       <c r="I21" s="47" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J21" s="48" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K21" s="49"/>
-    </row>
-    <row r="22" spans="2:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="L21" s="52"/>
+    </row>
+    <row r="22" spans="1:12" ht="112" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3</v>
+      </c>
       <c r="B22" s="47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D22" s="47" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="E22" s="47">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F22" s="47"/>
       <c r="G22" s="47"/>
       <c r="H22" s="47"/>
       <c r="I22" s="47" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J22" s="48" t="s">
-        <v>313</v>
-      </c>
-      <c r="K22" s="49"/>
-    </row>
-    <row r="23" spans="2:11" ht="112" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+      <c r="K22" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="L22" s="52"/>
+    </row>
+    <row r="23" spans="1:12" ht="192" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>4</v>
+      </c>
       <c r="B23" s="47" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D23" s="47" t="s">
         <v>90</v>
@@ -5841,66 +6539,57 @@
       <c r="G23" s="47"/>
       <c r="H23" s="47"/>
       <c r="I23" s="47" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J23" s="48" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" ht="192" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="L23" s="52"/>
+    </row>
+    <row r="24" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>2</v>
+      </c>
       <c r="B24" s="47" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E24" s="47">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F24" s="47"/>
       <c r="G24" s="47"/>
       <c r="H24" s="47"/>
       <c r="I24" s="47" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J24" s="48" t="s">
-        <v>315</v>
-      </c>
-      <c r="K24" s="50" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="B25" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="47">
-        <v>8</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="K24" s="49"/>
+      <c r="L24" s="52"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
       <c r="F25" s="47"/>
       <c r="G25" s="47"/>
       <c r="H25" s="47"/>
-      <c r="I25" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="J25" s="48" t="s">
-        <v>316</v>
-      </c>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
       <c r="K25" s="49"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B26" s="47"/>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -5912,7 +6601,7 @@
       <c r="J26" s="47"/>
       <c r="K26" s="49"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -5924,19 +6613,8 @@
       <c r="J27" s="47"/>
       <c r="K27" s="49"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="49"/>
-    </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0078D7 Classification : Internal</oddFooter>
@@ -5945,4 +6623,956 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871BA576-9EC2-314A-8156-BC19FA31C011}">
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="58.33203125" customWidth="1"/>
+    <col min="6" max="6" width="66.6640625" customWidth="1"/>
+    <col min="7" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="56" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+    </row>
+    <row r="4" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="57" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>377</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>378</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>381</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>382</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="58">
+        <v>1</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>391</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="I5" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="61">
+        <v>2</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>388</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>393</v>
+      </c>
+      <c r="F6" s="84" t="s">
+        <v>493</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="I6" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="58">
+        <v>3</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>395</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="I7" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="61">
+        <v>4</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>396</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="62" t="s">
+        <v>397</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>398</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="I8" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="58">
+        <v>5</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>399</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>400</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>401</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="I9" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="64">
+        <v>6</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>403</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>404</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="65" t="s">
+        <v>405</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>406</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>386</v>
+      </c>
+      <c r="H10" s="64" t="s">
+        <v>387</v>
+      </c>
+      <c r="I10" s="71" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="58">
+        <v>7</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>403</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>408</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>409</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="I11" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="61">
+        <v>8</v>
+      </c>
+      <c r="B12" s="62" t="s">
+        <v>403</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>411</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>412</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="78">
+        <v>11</v>
+      </c>
+      <c r="B13" s="79" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>420</v>
+      </c>
+      <c r="D13" s="78" t="s">
+        <v>421</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>422</v>
+      </c>
+      <c r="F13" s="79" t="s">
+        <v>423</v>
+      </c>
+      <c r="G13" s="78" t="s">
+        <v>386</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>386</v>
+      </c>
+      <c r="I13" s="77" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="61">
+        <v>12</v>
+      </c>
+      <c r="B14" s="62" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>424</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>426</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>427</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="67">
+        <v>13</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>419</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>425</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>429</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>430</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>402</v>
+      </c>
+      <c r="H15" s="67" t="s">
+        <v>386</v>
+      </c>
+      <c r="I15" s="71" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="74">
+        <v>16</v>
+      </c>
+      <c r="B16" s="75" t="s">
+        <v>437</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>438</v>
+      </c>
+      <c r="D16" s="74" t="s">
+        <v>439</v>
+      </c>
+      <c r="E16" s="75" t="s">
+        <v>440</v>
+      </c>
+      <c r="F16" s="75" t="s">
+        <v>441</v>
+      </c>
+      <c r="G16" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="H16" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="I16" s="77" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="58">
+        <v>17</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>437</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>442</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>439</v>
+      </c>
+      <c r="E17" s="59" t="s">
+        <v>443</v>
+      </c>
+      <c r="F17" s="59" t="s">
+        <v>444</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="61">
+        <v>22</v>
+      </c>
+      <c r="B18" s="62" t="s">
+        <v>454</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>458</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>459</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>460</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>402</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="I18" s="70" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="74">
+        <v>24</v>
+      </c>
+      <c r="B19" s="75" t="s">
+        <v>464</v>
+      </c>
+      <c r="C19" s="76" t="s">
+        <v>465</v>
+      </c>
+      <c r="D19" s="74" t="s">
+        <v>466</v>
+      </c>
+      <c r="E19" s="75" t="s">
+        <v>467</v>
+      </c>
+      <c r="F19" s="75" t="s">
+        <v>468</v>
+      </c>
+      <c r="G19" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="H19" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="I19" s="77" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="67">
+        <v>29</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>483</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>484</v>
+      </c>
+      <c r="D20" s="67" t="s">
+        <v>485</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>486</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>487</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>386</v>
+      </c>
+      <c r="H20" s="67" t="s">
+        <v>488</v>
+      </c>
+      <c r="I20" s="71" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="74">
+        <v>30</v>
+      </c>
+      <c r="B21" s="75" t="s">
+        <v>483</v>
+      </c>
+      <c r="C21" s="76" t="s">
+        <v>489</v>
+      </c>
+      <c r="D21" s="74" t="s">
+        <v>485</v>
+      </c>
+      <c r="E21" s="75" t="s">
+        <v>490</v>
+      </c>
+      <c r="F21" s="75" t="s">
+        <v>491</v>
+      </c>
+      <c r="G21" s="74" t="s">
+        <v>488</v>
+      </c>
+      <c r="H21" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="I21" s="77" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="58">
+        <v>9</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>403</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>413</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="F22" s="59" t="s">
+        <v>415</v>
+      </c>
+      <c r="G22" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="I22" s="72" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="74">
+        <v>10</v>
+      </c>
+      <c r="B23" s="75" t="s">
+        <v>403</v>
+      </c>
+      <c r="C23" s="76" t="s">
+        <v>416</v>
+      </c>
+      <c r="D23" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>417</v>
+      </c>
+      <c r="F23" s="75" t="s">
+        <v>418</v>
+      </c>
+      <c r="G23" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="H23" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="I23" s="81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="61">
+        <v>14</v>
+      </c>
+      <c r="B24" s="62" t="s">
+        <v>419</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>431</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>432</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>433</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>402</v>
+      </c>
+      <c r="I24" s="72" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="67">
+        <v>15</v>
+      </c>
+      <c r="B25" s="68" t="s">
+        <v>419</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>434</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="68" t="s">
+        <v>435</v>
+      </c>
+      <c r="F25" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>386</v>
+      </c>
+      <c r="H25" s="67" t="s">
+        <v>387</v>
+      </c>
+      <c r="I25" s="73" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="74">
+        <v>18</v>
+      </c>
+      <c r="B26" s="75" t="s">
+        <v>437</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>445</v>
+      </c>
+      <c r="D26" s="74" t="s">
+        <v>439</v>
+      </c>
+      <c r="E26" s="75" t="s">
+        <v>446</v>
+      </c>
+      <c r="F26" s="75" t="s">
+        <v>447</v>
+      </c>
+      <c r="G26" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="H26" s="74" t="s">
+        <v>386</v>
+      </c>
+      <c r="I26" s="81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="58">
+        <v>19</v>
+      </c>
+      <c r="B27" s="59" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>448</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>439</v>
+      </c>
+      <c r="E27" s="59" t="s">
+        <v>449</v>
+      </c>
+      <c r="F27" s="59" t="s">
+        <v>450</v>
+      </c>
+      <c r="G27" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="I27" s="72" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="64">
+        <v>20</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="66" t="s">
+        <v>451</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>439</v>
+      </c>
+      <c r="E28" s="65" t="s">
+        <v>452</v>
+      </c>
+      <c r="F28" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="G28" s="64" t="s">
+        <v>387</v>
+      </c>
+      <c r="H28" s="64" t="s">
+        <v>387</v>
+      </c>
+      <c r="I28" s="73" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="78">
+        <v>21</v>
+      </c>
+      <c r="B29" s="79" t="s">
+        <v>454</v>
+      </c>
+      <c r="C29" s="80" t="s">
+        <v>455</v>
+      </c>
+      <c r="D29" s="78" t="s">
+        <v>425</v>
+      </c>
+      <c r="E29" s="79" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="79" t="s">
+        <v>457</v>
+      </c>
+      <c r="G29" s="78" t="s">
+        <v>402</v>
+      </c>
+      <c r="H29" s="78" t="s">
+        <v>387</v>
+      </c>
+      <c r="I29" s="81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="67">
+        <v>23</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>454</v>
+      </c>
+      <c r="C30" s="69" t="s">
+        <v>461</v>
+      </c>
+      <c r="D30" s="67" t="s">
+        <v>425</v>
+      </c>
+      <c r="E30" s="68" t="s">
+        <v>462</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>402</v>
+      </c>
+      <c r="H30" s="67" t="s">
+        <v>386</v>
+      </c>
+      <c r="I30" s="73" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="78">
+        <v>25</v>
+      </c>
+      <c r="B31" s="79" t="s">
+        <v>464</v>
+      </c>
+      <c r="C31" s="80" t="s">
+        <v>469</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>470</v>
+      </c>
+      <c r="E31" s="79" t="s">
+        <v>471</v>
+      </c>
+      <c r="F31" s="79" t="s">
+        <v>472</v>
+      </c>
+      <c r="G31" s="78" t="s">
+        <v>402</v>
+      </c>
+      <c r="H31" s="78" t="s">
+        <v>386</v>
+      </c>
+      <c r="I31" s="81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="74">
+        <v>26</v>
+      </c>
+      <c r="B32" s="75" t="s">
+        <v>473</v>
+      </c>
+      <c r="C32" s="76" t="s">
+        <v>474</v>
+      </c>
+      <c r="D32" s="74" t="s">
+        <v>439</v>
+      </c>
+      <c r="E32" s="75" t="s">
+        <v>475</v>
+      </c>
+      <c r="F32" s="75" t="s">
+        <v>476</v>
+      </c>
+      <c r="G32" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="H32" s="74" t="s">
+        <v>387</v>
+      </c>
+      <c r="I32" s="81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="67">
+        <v>27</v>
+      </c>
+      <c r="B33" s="68" t="s">
+        <v>473</v>
+      </c>
+      <c r="C33" s="69" t="s">
+        <v>477</v>
+      </c>
+      <c r="D33" s="67" t="s">
+        <v>439</v>
+      </c>
+      <c r="E33" s="68" t="s">
+        <v>478</v>
+      </c>
+      <c r="F33" s="68" t="s">
+        <v>479</v>
+      </c>
+      <c r="G33" s="67" t="s">
+        <v>387</v>
+      </c>
+      <c r="H33" s="67" t="s">
+        <v>387</v>
+      </c>
+      <c r="I33" s="83" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="61">
+        <v>28</v>
+      </c>
+      <c r="B34" s="62" t="s">
+        <v>473</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>480</v>
+      </c>
+      <c r="D34" s="61" t="s">
+        <v>439</v>
+      </c>
+      <c r="E34" s="62" t="s">
+        <v>481</v>
+      </c>
+      <c r="F34" s="62" t="s">
+        <v>482</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>402</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="I34" s="82" t="s">
+        <v>492</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>